--- a/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>혼자여도 상 차려 먹기</t>
+          <t>대충 때우지 않고 차려 먹기</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="I204" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J204" s="4" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>혼밥에도 채소 한 가지</t>
+          <t>간단히 먹어도 채소 하나</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 채소 반찬을 준비해 봐요.</t>
+          <t>간단한 식사에도 채소 반찬을 준비해 봐요.</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="I206" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J206" s="4" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>도시락에 채소 한 칸</t>
+          <t>채소 반찬 미리 담기</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="I208" s="1" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J208" s="4" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>도시락에 달걀 하나</t>
+          <t>달걀 반찬 하나 챙기기</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="I209" s="1" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J209" s="4" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>도시락 국물은 빼기</t>
+          <t>국물 반찬은 빼고 담기</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="I210" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>도시락 반찬은 구이로</t>
+          <t>반찬은 튀김 대신 구이로</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>도시락 반찬의 조리법을 바꿔 보는 행동이에요.</t>
+          <t>반찬의 조리법을 바꿔 보는 행동이에요.</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="I211" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J211" s="4" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>가족 반찬에 채소 하나</t>
+          <t>상 차릴 때 채소 하나 더</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>함께 먹는 반찬이 늘면 나도 늘어요.</t>
+          <t>상에 오르는 채소가 늘면 먹는 채소도 늘어요.</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="I212" s="1" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J212" s="4" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>국은 각자 그릇에 덜기</t>
+          <t>국은 그릇에 덜어 먹기</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>각자 덜어 실제 먹는 양을 살펴봐요.</t>
+          <t>그릇에 덜어 실제 먹는 양을 살펴봐요.</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="I213" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J213" s="4" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>면 국물은 반만</t>
+          <t>국물 음식은 절반만</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>면 국물의 섭취량을 줄여 봐요.</t>
+          <t>국물 섭취량을 줄여 봐요.</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>함께 먹는 끼니 정하기</t>
+          <t>하루 한 끼는 여유 있게</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
-          <t>함께 먹으면 천천히, 즐겁게 먹게 돼요.</t>
+          <t>끼니 하나를 정해 두면 천천히 즐겁게 먹게 돼요.</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="I280" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 천천히 먹기와 포만감(식사 속도 연구)</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 천천히 먹기와 포만감(식사 속도 연구) · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J280" s="4" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>면 요리에 채소 넣기</t>
+          <t>끓일 때 채소 한 줌 넣기</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="I296" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 채소 등 다양한 식품 골고루 · WHO 채소·과일 하루 400g 이상 권고 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 채소 등 다양한 식품 골고루 · WHO 채소·과일 하루 400g 이상 권고 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>도시락에 단백질 담기</t>
+          <t>내일 단백질 반찬 담기</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
-          <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
+          <t>미리 담아 두면 밖에서도 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="I330" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 2020 한국인 영양소 섭취기준(단백질 끼니별 고른 섭취)</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 2020 한국인 영양소 섭취기준(단백질 끼니별 고른 섭취) · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="J330" s="4" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>면 요리에 콩나물 한 줌</t>
+          <t>끓일 때 콩나물 한 줌</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="E346" s="4" t="inlineStr">
         <is>
-          <t>콩나물을 넣으면 면 요리에도 채소가 더해져요.</t>
+          <t>콩나물을 넣으면 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="I346" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 채소 등 다양한 식품 골고루 · WHO 채소·과일 하루 400g 이상 권고 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 채소 등 다양한 식품 골고루 · WHO 채소·과일 하루 400g 이상 권고 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="J346" s="4" t="inlineStr">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>면 요리에 달걀 하나</t>
+          <t>끓일 때 달걀 하나 넣기</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>달걀을 넣으면 면 요리에도 단백질이 더해져요.</t>
+          <t>달걀을 넣으면 한 그릇에 단백질이 더해져요.</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="I349" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 2020 한국인 영양소 섭취기준(단백질 끼니별 고른 섭취) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 1. 다양한 식품 골고루 · 2020 한국인 영양소 섭취기준(단백질 끼니별 고른 섭취) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="J349" s="4" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>분말 스프는 반만</t>
+          <t>양념은 절반만 넣기</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>스프를 반만 넣으면 나트륨이 크게 줄어요.</t>
+          <t>양념을 반만 넣으면 나트륨이 크게 줄어요.</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="I355" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 4. 덜 짜게 · WHO 나트륨 하루 2,000mg 미만 권고 · 국·찌개가 나트륨 주 공급원(국민건강영양조사) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 4. 덜 짜게 · WHO 나트륨 하루 2,000mg 미만 권고 · 국·찌개가 나트륨 주 공급원(국민건강영양조사) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="J355" s="4" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -16365,7 +16365,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>저녁은 매일 7시쯤</t>
+          <t>저녁은 매일 같은 시간에</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="I277" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 위식도역류 생활수칙(대한소화기학회): 잠들기 전 식사 피하기</t>
+          <t>10-13 신규. 근거: 국민 공통 식생활지침(보건복지부 2021) 3. 과식 피하기 · 위식도역류 생활수칙(대한소화기학회): 잠들기 전 식사 피하기 · 10-19 특정 시각 전제 없이</t>
         </is>
       </c>
       <c r="J277" s="4" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -3198,7 +3198,7 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>외식에도 채소 하나 더</t>
+          <t>외식 메뉴는 채소 위주로</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>외식할 때 채소 메뉴가 있는지 살펴봐요.</t>
+          <t>채소가 많은 메뉴를 고르면 외식에서도 채소를 챙겨요.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -3198,7 +3198,7 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>외식 메뉴는 채소 위주로</t>
+          <t>외식 메뉴, 채소 곁들이기</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>채소가 많은 메뉴를 고르면 외식에서도 채소를 챙겨요.</t>
+          <t>채소를 곁들이면 외식에서도 채소를 챙겨요.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로 · 10-19 외식 메뉴에 채소 곁들이기로</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -14484,7 +14484,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>먹기 편한 시간 적기</t>
+          <t>먹기 편한 시간 적어보기</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="I244" s="1" t="inlineStr">
         <is>
-          <t>10-13 신규. 근거: 식욕이 없을 때 식사 요령(대한영양사협회 · 국가암정보센터): 조금씩 자주, 먹기 편한 음식부터</t>
+          <t>10-13 신규. 근거: 식욕이 없을 때 식사 요령(대한영양사협회 · 국가암정보센터): 조금씩 자주, 먹기 편한 음식부터 · 10-19 「적어보기」로</t>
         </is>
       </c>
       <c r="J244" s="4" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -67,6 +67,10 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D92D20"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -94,7 +98,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
@@ -124,6 +128,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1144,9 +1151,9 @@
           <t>단 음료 한 번은 물로 바꾸기</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>한 잔은 물로 바꾸기</t>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>단 음료 대신 물 한 잔</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
